--- a/data/trans_orig/P2A_ner_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17650</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38331</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>256315</t>
+          <t>255354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267768</t>
+          <t>267675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234334</t>
+          <t>234349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251069</t>
+          <t>251451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>495517</t>
+          <t>495430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>516198</t>
+          <t>515273</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>11356</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29593</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>18489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40849</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>35317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61671</t>
+          <t>62245</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>463482</t>
+          <t>465948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481964</t>
+          <t>481719</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463100</t>
+          <t>464482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>484787</t>
+          <t>485460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>935353</t>
+          <t>934779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>962223</t>
+          <t>961707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8744</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>313947</t>
+          <t>314014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327681</t>
+          <t>327662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334504</t>
+          <t>334507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645514</t>
+          <t>644740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653288</t>
+          <t>653261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32076</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345043</t>
+          <t>343801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355948</t>
+          <t>355289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>347698</t>
+          <t>346774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362358</t>
+          <t>362193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>698051</t>
+          <t>698906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>715585</t>
+          <t>716608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33380</t>
+          <t>33785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>189228</t>
+          <t>187776</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199002</t>
+          <t>199515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>183708</t>
+          <t>184099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199032</t>
+          <t>198967</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377596</t>
+          <t>377191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395856</t>
+          <t>396180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>18017</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8028</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23566</t>
+          <t>23057</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261476</t>
+          <t>261603</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269776</t>
+          <t>269833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260196</t>
+          <t>260127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273312</t>
+          <t>273191</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525389</t>
+          <t>525898</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540927</t>
+          <t>540853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>13872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>31916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44916</t>
+          <t>46453</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596107</t>
+          <t>596757</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>608851</t>
+          <t>609432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>605679</t>
+          <t>606303</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>623822</t>
+          <t>624347</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1208330</t>
+          <t>1206793</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1230640</t>
+          <t>1230368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46861</t>
+          <t>44041</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32907</t>
+          <t>32554</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60562</t>
+          <t>59707</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>60085</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>98786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>696934</t>
+          <t>699754</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>720983</t>
+          <t>721547</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>722949</t>
+          <t>723804</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>750604</t>
+          <t>750957</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1431922</t>
+          <t>1428520</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1468114</t>
+          <t>1467221</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>73626</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>111320</t>
+          <t>110999</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>129417</t>
+          <t>132695</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>181201</t>
+          <t>182661</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>216538</t>
+          <t>217358</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>278899</t>
+          <t>277457</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3165223</t>
+          <t>3165544</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3203898</t>
+          <t>3202917</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3197996</t>
+          <t>3196536</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3249780</t>
+          <t>3246502</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6376842</t>
+          <t>6378284</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6439203</t>
+          <t>6438383</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27864</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19789</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41341</t>
+          <t>40635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>276395</t>
+          <t>277342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289138</t>
+          <t>289387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259381</t>
+          <t>259841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276068</t>
+          <t>277043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540642</t>
+          <t>541348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562194</t>
+          <t>562338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27137</t>
+          <t>25572</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>21493</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>42975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32828</t>
+          <t>33885</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63022</t>
+          <t>63298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>478390</t>
+          <t>479955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497556</t>
+          <t>497580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480109</t>
+          <t>480790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502667</t>
+          <t>502272</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>966270</t>
+          <t>965994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>996464</t>
+          <t>995407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>22688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309543</t>
+          <t>308885</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320389</t>
+          <t>320220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327740</t>
+          <t>327488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338136</t>
+          <t>338831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641220</t>
+          <t>642378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>657056</t>
+          <t>657274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17289</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>24143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45094</t>
+          <t>45527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31405</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56749</t>
+          <t>55152</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356693</t>
+          <t>356410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369061</t>
+          <t>369074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343857</t>
+          <t>343424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364233</t>
+          <t>364808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706184</t>
+          <t>707781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>731528</t>
+          <t>731388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>31805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>41711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38745</t>
+          <t>37893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66315</t>
+          <t>66527</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>181565</t>
+          <t>180813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199533</t>
+          <t>200054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177233</t>
+          <t>177880</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198189</t>
+          <t>198397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365894</t>
+          <t>365682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>393464</t>
+          <t>394316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269195</t>
+          <t>269272</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>263007</t>
+          <t>262651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275075</t>
+          <t>275094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>535550</t>
+          <t>535744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548143</t>
+          <t>548310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28662</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25389</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>24394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47727</t>
+          <t>46955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>634126</t>
+          <t>635329</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651195</t>
+          <t>651129</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>668464</t>
+          <t>667675</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>685244</t>
+          <t>684849</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1308914</t>
+          <t>1309686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1332905</t>
+          <t>1332247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>37501</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41585</t>
+          <t>43254</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>40341</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71246</t>
+          <t>71684</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>743224</t>
+          <t>741597</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764245</t>
+          <t>764465</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>782268</t>
+          <t>780599</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>803558</t>
+          <t>802871</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1531705</t>
+          <t>1531267</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1564084</t>
+          <t>1562610</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84953</t>
+          <t>87233</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>125556</t>
+          <t>129412</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>152205</t>
+          <t>150646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207429</t>
+          <t>204182</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>247516</t>
+          <t>250421</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>314833</t>
+          <t>316364</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3301223</t>
+          <t>3297367</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3341826</t>
+          <t>3339546</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3350880</t>
+          <t>3354127</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3406104</t>
+          <t>3407663</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6670255</t>
+          <t>6668724</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6737572</t>
+          <t>6734667</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32459</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34333</t>
+          <t>34941</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60094</t>
+          <t>61683</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53462</t>
+          <t>53805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86795</t>
+          <t>88106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261302</t>
+          <t>259495</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279179</t>
+          <t>279395</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228609</t>
+          <t>227020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254370</t>
+          <t>253762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>495669</t>
+          <t>494358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>529002</t>
+          <t>528659</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26428</t>
+          <t>25722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39821</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68473</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54783</t>
+          <t>54718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88676</t>
+          <t>86906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476147</t>
+          <t>476853</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493101</t>
+          <t>493030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>454611</t>
+          <t>454659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483263</t>
+          <t>482981</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936983</t>
+          <t>938753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970876</t>
+          <t>970941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43260</t>
+          <t>42204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26795</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51638</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305595</t>
+          <t>306278</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315740</t>
+          <t>316321</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293049</t>
+          <t>294105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314780</t>
+          <t>314979</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>603236</t>
+          <t>604728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628079</t>
+          <t>628023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>23066</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45411</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37668</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65748</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>342893</t>
+          <t>341489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359807</t>
+          <t>359901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341872</t>
+          <t>342855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364460</t>
+          <t>364217</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691499</t>
+          <t>691589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719579</t>
+          <t>719126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>9613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24330</t>
+          <t>24663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41384</t>
+          <t>42154</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34576</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58463</t>
+          <t>58825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186891</t>
+          <t>186558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202388</t>
+          <t>201608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177203</t>
+          <t>176433</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>197949</t>
+          <t>198217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371345</t>
+          <t>370983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395232</t>
+          <t>395486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19511</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45139</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33280</t>
+          <t>31970</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59023</t>
+          <t>59604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243612</t>
+          <t>244411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256612</t>
+          <t>256840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227976</t>
+          <t>228017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249694</t>
+          <t>249595</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>477215</t>
+          <t>476634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502958</t>
+          <t>504268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18058</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41708</t>
+          <t>39958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59779</t>
+          <t>62075</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93058</t>
+          <t>96755</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84291</t>
+          <t>84708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125289</t>
+          <t>126636</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>614850</t>
+          <t>616600</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638500</t>
+          <t>638198</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>598236</t>
+          <t>594539</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>631515</t>
+          <t>629219</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1222563</t>
+          <t>1221216</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1263561</t>
+          <t>1263144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26602</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50495</t>
+          <t>50147</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69911</t>
+          <t>71021</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107187</t>
+          <t>107887</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102399</t>
+          <t>102817</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>147841</t>
+          <t>150152</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>728088</t>
+          <t>728436</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>751981</t>
+          <t>752161</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>718980</t>
+          <t>718280</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>756256</t>
+          <t>755146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1456909</t>
+          <t>1454598</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1502351</t>
+          <t>1501933</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130162</t>
+          <t>129217</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>179186</t>
+          <t>177646</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>354888</t>
+          <t>351692</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>430916</t>
+          <t>431385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>495007</t>
+          <t>502869</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>591483</t>
+          <t>592778</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3215164</t>
+          <t>3216704</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3264188</t>
+          <t>3265133</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3113626</t>
+          <t>3113157</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3189654</t>
+          <t>3192850</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6347409</t>
+          <t>6346114</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6443885</t>
+          <t>6436023</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023</t>
+          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20743</t>
+          <t>20990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>11149</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>27838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290700</t>
+          <t>290453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305294</t>
+          <t>305686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278411</t>
+          <t>278283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285835</t>
+          <t>285629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>572918</t>
+          <t>573239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589329</t>
+          <t>589928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22914</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>40845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34080</t>
+          <t>33752</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58108</t>
+          <t>57904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>497229</t>
+          <t>496384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511569</t>
+          <t>512042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>473891</t>
+          <t>474124</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492055</t>
+          <t>491887</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>975251</t>
+          <t>975455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>999279</t>
+          <t>999607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21486</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>20957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40881</t>
+          <t>40918</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294564</t>
+          <t>296024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310319</t>
+          <t>310134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323775</t>
+          <t>323842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336906</t>
+          <t>336748</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624297</t>
+          <t>624260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644037</t>
+          <t>644221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29946</t>
+          <t>29491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>22548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>50209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282611</t>
+          <t>283066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302049</t>
+          <t>302054</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448701</t>
+          <t>447118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466973</t>
+          <t>466829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>736231</t>
+          <t>738065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>764552</t>
+          <t>765726</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172286</t>
+          <t>172395</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178071</t>
+          <t>178075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>248781</t>
+          <t>248618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>255857</t>
+          <t>256088</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424664</t>
+          <t>424542</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>433014</t>
+          <t>432913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15274</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28544</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252338</t>
+          <t>252020</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263494</t>
+          <t>263414</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241782</t>
+          <t>241616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250914</t>
+          <t>250890</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498148</t>
+          <t>497970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>512699</t>
+          <t>512475</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>21309</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47199</t>
+          <t>44942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>509972</t>
+          <t>546999</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76424</t>
+          <t>76028</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>752279</t>
+          <t>692333</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>46,98%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577080</t>
+          <t>579337</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>603750</t>
+          <t>602970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>339293</t>
+          <t>302266</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>800803</t>
+          <t>801391</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>721265</t>
+          <t>781211</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1397120</t>
+          <t>1397516</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26724</t>
+          <t>26633</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21952</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39271</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28961</t>
+          <t>27359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61814</t>
+          <t>62073</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>901996</t>
+          <t>902087</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>922285</t>
+          <t>922262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>678460</t>
+          <t>678244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695779</t>
+          <t>695699</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1584638</t>
+          <t>1584379</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1617491</t>
+          <t>1619093</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>88845</t>
+          <t>82858</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>141740</t>
+          <t>137277</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161276</t>
+          <t>161437</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>988032</t>
+          <t>979354</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>268313</t>
+          <t>271451</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1189282</t>
+          <t>1132535</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3318077</t>
+          <t>3322540</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3370972</t>
+          <t>3376959</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2724248</t>
+          <t>2732926</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3551004</t>
+          <t>3550843</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5982815</t>
+          <t>6039562</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6903784</t>
+          <t>6900646</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_ner_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>25625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>39297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>255354</t>
+          <t>255222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267675</t>
+          <t>268420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>234349</t>
+          <t>235213</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251451</t>
+          <t>251294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>495430</t>
+          <t>494551</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515273</t>
+          <t>515981</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11356</t>
+          <t>11662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27127</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39467</t>
+          <t>40118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35317</t>
+          <t>35125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62245</t>
+          <t>62107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465948</t>
+          <t>464953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>481719</t>
+          <t>481413</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464482</t>
+          <t>463831</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>485460</t>
+          <t>484527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>934779</t>
+          <t>934917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>961707</t>
+          <t>961899</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314014</t>
+          <t>314224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327662</t>
+          <t>326870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334507</t>
+          <t>334498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>644740</t>
+          <t>645479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653261</t>
+          <t>653274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>24104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31221</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343801</t>
+          <t>343551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>355289</t>
+          <t>355909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346774</t>
+          <t>347352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362193</t>
+          <t>362163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>698906</t>
+          <t>697738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>716608</t>
+          <t>716346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14796</t>
+          <t>15079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187776</t>
+          <t>188823</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>199515</t>
+          <t>199005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184099</t>
+          <t>182968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198967</t>
+          <t>198961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>377191</t>
+          <t>377028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396180</t>
+          <t>395897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>17069</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261603</t>
+          <t>261909</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269833</t>
+          <t>269786</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260127</t>
+          <t>261075</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273191</t>
+          <t>273367</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>525898</t>
+          <t>527131</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540853</t>
+          <t>541160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>45485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>596757</t>
+          <t>596677</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>609432</t>
+          <t>609599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>606303</t>
+          <t>604963</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>624347</t>
+          <t>623882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1206793</t>
+          <t>1207761</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1230368</t>
+          <t>1230166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44041</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59707</t>
+          <t>61067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60085</t>
+          <t>59248</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98786</t>
+          <t>96262</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>699754</t>
+          <t>698829</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>721547</t>
+          <t>721853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>723804</t>
+          <t>722444</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>750957</t>
+          <t>749751</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1428520</t>
+          <t>1431044</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1467221</t>
+          <t>1468058</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>73626</t>
+          <t>74179</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>110999</t>
+          <t>109749</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132695</t>
+          <t>129995</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>182661</t>
+          <t>181669</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>217358</t>
+          <t>215957</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>277457</t>
+          <t>278037</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3165544</t>
+          <t>3166794</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3202917</t>
+          <t>3202364</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3196536</t>
+          <t>3197528</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3246502</t>
+          <t>3249202</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6378284</t>
+          <t>6377704</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6438383</t>
+          <t>6439784</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>27737</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40635</t>
+          <t>39700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>277342</t>
+          <t>277274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289387</t>
+          <t>289567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259841</t>
+          <t>259508</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277043</t>
+          <t>276939</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>541348</t>
+          <t>542283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562338</t>
+          <t>563031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25572</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42975</t>
+          <t>44275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33885</t>
+          <t>34098</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63298</t>
+          <t>63122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>479955</t>
+          <t>478093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>497580</t>
+          <t>497589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480790</t>
+          <t>479490</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502272</t>
+          <t>502776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965994</t>
+          <t>966170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>995407</t>
+          <t>995194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15161</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,82 +4757,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6195</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2126</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13618</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>13853</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>7819</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>21777</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6195</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2189</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13532</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>13853</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7792</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>22688</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308885</t>
+          <t>309403</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>320220</t>
+          <t>320392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,82 +4870,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>334825</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>327402</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>338894</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,01%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>651213</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>643289</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>657247</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>98,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>334825</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>327488</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>338831</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>651213</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>642378</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>657274</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24143</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45527</t>
+          <t>45576</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55152</t>
+          <t>56137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356410</t>
+          <t>356883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369074</t>
+          <t>369066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343424</t>
+          <t>343375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364808</t>
+          <t>364416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>707781</t>
+          <t>706796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>731388</t>
+          <t>732548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>30728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21194</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41711</t>
+          <t>42091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>39082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66527</t>
+          <t>67229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180813</t>
+          <t>181890</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200054</t>
+          <t>199341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177880</t>
+          <t>177500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198397</t>
+          <t>198029</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365682</t>
+          <t>364980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394316</t>
+          <t>393127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17380</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269272</t>
+          <t>268864</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262651</t>
+          <t>262444</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275094</t>
+          <t>275006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>535744</t>
+          <t>534798</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548310</t>
+          <t>547965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>27529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26178</t>
+          <t>25438</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46955</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635329</t>
+          <t>635259</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>651129</t>
+          <t>651821</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>667675</t>
+          <t>668415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>684849</t>
+          <t>685052</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1309686</t>
+          <t>1309803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1332247</t>
+          <t>1333126</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37501</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>43254</t>
+          <t>42456</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40341</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71684</t>
+          <t>71390</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>741597</t>
+          <t>742522</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764465</t>
+          <t>764567</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>780599</t>
+          <t>781397</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>802871</t>
+          <t>803568</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1531267</t>
+          <t>1531561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1562610</t>
+          <t>1562909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87233</t>
+          <t>84969</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>129412</t>
+          <t>127591</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>150646</t>
+          <t>153299</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>204182</t>
+          <t>205236</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>250421</t>
+          <t>246593</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>316364</t>
+          <t>316238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3297367</t>
+          <t>3299188</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3339546</t>
+          <t>3341810</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3354127</t>
+          <t>3353073</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3407663</t>
+          <t>3405010</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6668724</t>
+          <t>6668850</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6734667</t>
+          <t>6738495</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34266</t>
+          <t>32577</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34941</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61683</t>
+          <t>60977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53805</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88106</t>
+          <t>86954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>259495</t>
+          <t>261184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>279395</t>
+          <t>279886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227020</t>
+          <t>227726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253762</t>
+          <t>252852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>494358</t>
+          <t>495510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>528659</t>
+          <t>528477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25722</t>
+          <t>25702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40103</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68425</t>
+          <t>69481</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54718</t>
+          <t>54984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86906</t>
+          <t>88446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>476853</t>
+          <t>476873</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493030</t>
+          <t>493155</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>454659</t>
+          <t>453603</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482981</t>
+          <t>482654</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>938753</t>
+          <t>937213</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>970941</t>
+          <t>970675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42204</t>
+          <t>42047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50146</t>
+          <t>49861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306278</t>
+          <t>306106</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316321</t>
+          <t>315764</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294105</t>
+          <t>294262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314979</t>
+          <t>315370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>604728</t>
+          <t>605013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628023</t>
+          <t>628991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23066</t>
+          <t>23021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>64852</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341489</t>
+          <t>342321</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359901</t>
+          <t>359718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342855</t>
+          <t>341543</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364217</t>
+          <t>364262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691589</t>
+          <t>692395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719126</t>
+          <t>719076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24663</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42154</t>
+          <t>40877</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34322</t>
+          <t>34126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58825</t>
+          <t>59601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>186558</t>
+          <t>187800</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201608</t>
+          <t>201898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>176433</t>
+          <t>177710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198217</t>
+          <t>197579</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>370983</t>
+          <t>370207</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395486</t>
+          <t>395682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>19995</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23520</t>
+          <t>23227</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>45310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31970</t>
+          <t>32155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59604</t>
+          <t>58721</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244411</t>
+          <t>243128</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>256840</t>
+          <t>256975</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>228017</t>
+          <t>227805</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249595</t>
+          <t>249888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>476634</t>
+          <t>477517</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>504268</t>
+          <t>504083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39958</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62075</t>
+          <t>60440</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96755</t>
+          <t>94501</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84708</t>
+          <t>86271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126636</t>
+          <t>128806</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>616600</t>
+          <t>616161</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>638198</t>
+          <t>637452</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594539</t>
+          <t>596793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>629219</t>
+          <t>630854</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1221216</t>
+          <t>1219046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1263144</t>
+          <t>1261581</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50147</t>
+          <t>48734</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71021</t>
+          <t>70905</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>107887</t>
+          <t>106716</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>102817</t>
+          <t>104253</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150152</t>
+          <t>149042</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>728436</t>
+          <t>729849</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>752161</t>
+          <t>752107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>718280</t>
+          <t>719451</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>755146</t>
+          <t>755262</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1454598</t>
+          <t>1455708</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1501933</t>
+          <t>1500497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129217</t>
+          <t>130715</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>177646</t>
+          <t>179509</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>351692</t>
+          <t>352922</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>431385</t>
+          <t>429414</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>502869</t>
+          <t>500698</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>592778</t>
+          <t>595868</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3216704</t>
+          <t>3214841</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3265133</t>
+          <t>3263635</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3113157</t>
+          <t>3115128</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3192850</t>
+          <t>3191620</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6346114</t>
+          <t>6343024</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6436023</t>
+          <t>6438194</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11361</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18265</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27838</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>300082</t>
+          <t>308657</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290453</t>
+          <t>301440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305686</t>
+          <t>313470</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>282731</t>
+          <t>308110</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278283</t>
+          <t>302667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285629</t>
+          <t>311409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>582812</t>
+          <t>616767</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573239</t>
+          <t>608198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589928</t>
+          <t>622948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23082</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40845</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43643</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57904</t>
+          <t>58585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505588</t>
+          <t>517471</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496384</t>
+          <t>508583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>512042</t>
+          <t>523814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>484128</t>
+          <t>514479</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474124</t>
+          <t>503964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491887</t>
+          <t>523054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>989716</t>
+          <t>1031950</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>975455</t>
+          <t>1018556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>999607</t>
+          <t>1042179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>18316</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25286</t>
+          <t>25935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40918</t>
+          <t>40094</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>304822</t>
+          <t>305436</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296024</t>
+          <t>295421</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>310134</t>
+          <t>310398</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>331077</t>
+          <t>338065</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323842</t>
+          <t>330446</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336748</t>
+          <t>344144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>635899</t>
+          <t>643502</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>624260</t>
+          <t>632281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644221</t>
+          <t>651098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29491</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>11494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>28318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>38026</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>25689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50209</t>
+          <t>53561</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>294681</t>
+          <t>353555</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283066</t>
+          <t>341012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302054</t>
+          <t>361650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>458872</t>
+          <t>403524</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447118</t>
+          <t>393643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466829</t>
+          <t>410467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>753552</t>
+          <t>757081</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738065</t>
+          <t>741546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>765726</t>
+          <t>769418</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>176699</t>
+          <t>203448</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172395</t>
+          <t>199616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178075</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>252641</t>
+          <t>222363</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>248618</t>
+          <t>218213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256088</t>
+          <t>225145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>429339</t>
+          <t>425810</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424542</t>
+          <t>420941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>432913</t>
+          <t>429163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17616</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>20267</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>28161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>259033</t>
+          <t>260575</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252020</t>
+          <t>254110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263414</t>
+          <t>264597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>247040</t>
+          <t>253615</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>241616</t>
+          <t>248424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250890</t>
+          <t>257324</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>506074</t>
+          <t>514190</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>497970</t>
+          <t>506296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>512475</t>
+          <t>519724</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>36845</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21309</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>52886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>244995</t>
+          <t>51805</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>40615</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>546999</t>
+          <t>65887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>275848</t>
+          <t>88650</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>70627</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>692333</t>
+          <t>107895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>593426</t>
+          <t>682842</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>579337</t>
+          <t>666801</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>602970</t>
+          <t>694332</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>604270</t>
+          <t>720252</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>302266</t>
+          <t>706170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>801391</t>
+          <t>731442</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1197696</t>
+          <t>1403094</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>781211</t>
+          <t>1383849</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1397516</t>
+          <t>1421117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>16356</t>
+          <t>19469</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>30569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29926</t>
+          <t>34515</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22032</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39487</t>
+          <t>45530</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>46282</t>
+          <t>53984</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27359</t>
+          <t>42530</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62073</t>
+          <t>69082</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>912364</t>
+          <t>778603</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>902087</t>
+          <t>767503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>922262</t>
+          <t>785455</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>687805</t>
+          <t>796816</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>678244</t>
+          <t>785801</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695699</t>
+          <t>805440</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1600170</t>
+          <t>1575419</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1584379</t>
+          <t>1560321</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1619093</t>
+          <t>1586873</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>113122</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>82858</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137277</t>
+          <t>148500</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>179728</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>161437</t>
+          <t>157768</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>979354</t>
+          <t>204755</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>476840</t>
+          <t>301902</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>271451</t>
+          <t>272941</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1132535</t>
+          <t>336245</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3346695</t>
+          <t>3410588</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3322540</t>
+          <t>3384262</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3376959</t>
+          <t>3431064</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3348563</t>
+          <t>3557226</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2732926</t>
+          <t>3532199</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3550843</t>
+          <t>3579186</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6695257</t>
+          <t>6967814</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6039562</t>
+          <t>6933471</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6900646</t>
+          <t>6996775</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_ner_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_ner_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con problemas de nervios, depresión o trastorno mental en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
